--- a/membership_forms/018_youth_mentoring_survey--membership_forms.xlsx
+++ b/membership_forms/018_youth_mentoring_survey--membership_forms.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -31,7 +32,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +43,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="004472C4"/>
         <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0070AD47"/>
+        <bgColor rgb="0070AD47"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,9 +64,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -427,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -510,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>page_1</t>
+          <t>contact_information</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>youth_mentoring_survey</t>
+          <t>Contact Information</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -533,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>page_2</t>
+          <t>participant_details</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>contact_information</t>
+          <t>Participant Details</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -556,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>page_3</t>
+          <t>program_details</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>program_details</t>
+          <t>Program Details</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -579,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>page_4</t>
+          <t>participant_engagement</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>survey_participant_details</t>
+          <t>Participant Engagement</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -597,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>page_5</t>
+          <t>participant_satisfaction</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>program_evaluation</t>
+          <t>Participant Satisfaction</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -625,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>page_6</t>
+          <t>participant_outcomes</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>survey_results</t>
+          <t>Participant Outcomes</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -648,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>page_7</t>
+          <t>program_goals</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>program_goals</t>
+          <t>Program Goals</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -671,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>page_8</t>
+          <t>participant_feedback</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>survey_implementation</t>
+          <t>Participant Feedback</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -694,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>page_9</t>
+          <t>program_evaluation</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>program_progress</t>
+          <t>Program Evaluation</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -717,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>page_10</t>
+          <t>program_progress</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>participant_engagement</t>
+          <t>Program Progress</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -740,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>page_11</t>
+          <t>participant_retention</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>participant_satisfaction</t>
+          <t>Participant Retention</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -763,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>page_12</t>
+          <t>program_fidelity</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>participant_outcomes</t>
+          <t>Program Fidelity</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -786,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>page_13</t>
+          <t>program_improvement</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>program_fidelity</t>
+          <t>Program Improvement</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -809,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>page_14</t>
+          <t>participant_satisfaction_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>participant_retention</t>
+          <t>Participant Satisfaction 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -827,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>page_15</t>
+          <t>program_outcomes_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>participant_feedback</t>
+          <t>Program Outcomes</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -855,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>page_16</t>
+          <t>program_engagement_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>program_evaluation</t>
+          <t>Program Engagement</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -878,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>page_17</t>
+          <t>participant_recommended</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>program_goals</t>
+          <t>Participant Recommended</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -901,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>page_18</t>
+          <t>participant_suggest</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>survey_results</t>
+          <t>Participant Suggest</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -919,17 +929,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>page_19</t>
+          <t>participant_outcomes_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>participant_outcomes</t>
+          <t>Participant Outcomes 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -947,131 +957,16 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>page_20</t>
+          <t>program_satisfaction_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>participant_satisfaction</t>
+          <t>Program Satisfaction</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>page_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>participant_engagement</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>page_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>participant_retention</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>page_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>participant_feedback</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>page_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>program_fidelity</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>page_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>participant_satisfaction</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1083,6 +978,229 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>list_name</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>participant_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>very_satisfied</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Very Satisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>participant_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>somewhat_satisfied</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Somewhat Satisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>participant_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>neither_satisfied_nor_dissatisfied</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Neither Satisfied Nor Dissatisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>participant_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>somewhat_dissatisfied</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Somewhat Dissatisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>participant_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>very_dissatisfied</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Very Dissatisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>program_outcomes_2_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>short-term_outcomes</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Short-term Outcomes</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>program_outcomes_2_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>long-term_outcomes</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Long-term Outcomes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>program_outcomes_2_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>no_outcomes</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>No Outcomes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>participant_outcomes_2_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>short-term_outcomes</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Short-term Outcomes</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>participant_outcomes_2_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>long-term_outcomes</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Long-term Outcomes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>participant_outcomes_2_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>no_outcomes</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>No Outcomes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
